--- a/Result/profitability/2538.xlsx
+++ b/Result/profitability/2538.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09999999999999991</v>
+        <v>0.1087499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>71.05125000000001</v>
+        <v>75.7675</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1787499999999999</v>
+        <v>0.1337499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>69.535</v>
+        <v>73.05</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1787499999999999</v>
+        <v>0.1724999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>66.175</v>
+        <v>68.86000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1999999999999999</v>
+        <v>0.2299999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>61.07375</v>
+        <v>60.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2699999999999999</v>
+        <v>0.1612499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>53.34375</v>
+        <v>53.01375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2249999999999999</v>
+        <v>0.2462499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>46.02625</v>
+        <v>44.4</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3099999999999999</v>
+        <v>0.3024999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>36.83625</v>
+        <v>35.34</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2538</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>74</v>
+      </c>
+      <c r="D75" t="n">
+        <v>12</v>
+      </c>
+      <c r="E75" t="n">
+        <v>62</v>
+      </c>
+      <c r="F75" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-39</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.06749999999999991</v>
+      </c>
+      <c r="N75" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-11.97</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1242990654205608</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8571428571428572</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.790000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.04300953245574224</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
